--- a/Plotting/Results_excels/production_shares_olefins_Scope1-3.xlsx
+++ b/Plotting/Results_excels/production_shares_olefins_Scope1-3.xlsx
@@ -539,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Conventional</t>
+          <t>Conventional (fossil)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
+          <t>Conventional (fossil) with CC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -620,22 +620,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1401265.181013603</v>
+        <v>1401265.181013409</v>
       </c>
       <c r="F6" t="n">
-        <v>602827.8937104597</v>
+        <v>602251.152275402</v>
       </c>
       <c r="G6" t="n">
-        <v>221185.4197186728</v>
+        <v>220608.8015750399</v>
       </c>
       <c r="H6" t="n">
-        <v>1401265.18101358</v>
+        <v>1401265.181013531</v>
       </c>
       <c r="I6" t="n">
-        <v>603806.4382143666</v>
+        <v>599676.7378626197</v>
       </c>
       <c r="J6" t="n">
-        <v>222160.8795700106</v>
+        <v>218040.6017796196</v>
       </c>
     </row>
     <row r="7">
@@ -691,19 +691,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>832311.6761443499</v>
+        <v>833670.5576873445</v>
       </c>
       <c r="G8" t="n">
-        <v>894271.2363347108</v>
+        <v>894343.0849953681</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3.790887603827287e-11</v>
       </c>
       <c r="I8" t="n">
-        <v>831090.3558850527</v>
+        <v>836776.7323536183</v>
       </c>
       <c r="J8" t="n">
-        <v>892473.7149865876</v>
+        <v>897964.6829518724</v>
       </c>
     </row>
     <row r="9">
@@ -722,22 +722,22 @@
         <v>-1.136217926629919e-10</v>
       </c>
       <c r="E9" t="n">
-        <v>316335.4517647082</v>
+        <v>316335.4517647216</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-6.250848758323563e-11</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.340789397460244e-11</v>
+        <v>-6.351994875963007e-11</v>
       </c>
       <c r="H9" t="n">
-        <v>316335.4517647056</v>
+        <v>316335.4517647061</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-6.239029452653497e-11</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.024058041087535e-11</v>
+        <v>-6.328592910603344e-11</v>
       </c>
     </row>
     <row r="10">
@@ -759,19 +759,19 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>282295.4611157335</v>
+        <v>281513.2013873534</v>
       </c>
       <c r="G10" t="n">
-        <v>601899.2194410748</v>
+        <v>602403.8693291809</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>282538.4398285086</v>
+        <v>280980.9071812385</v>
       </c>
       <c r="J10" t="n">
-        <v>602721.4832554583</v>
+        <v>601349.9385044341</v>
       </c>
     </row>
     <row r="11">
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1.423405253295114e-08</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
